--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/18.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/18.xlsx
@@ -426,13 +426,13 @@
         <v>-5.871185461096176</v>
       </c>
       <c r="E2">
-        <v>-20.81241124008579</v>
+        <v>-33.31910546972971</v>
       </c>
       <c r="F2">
-        <v>-3.490748666318652</v>
+        <v>-5.113760634949696</v>
       </c>
       <c r="G2">
-        <v>-13.67947161276264</v>
+        <v>-20.27360491897873</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.837293292167111</v>
       </c>
       <c r="E3">
-        <v>-21.58468814040588</v>
+        <v>-33.38289808307576</v>
       </c>
       <c r="F3">
-        <v>-3.585931394369927</v>
+        <v>-5.065666451910559</v>
       </c>
       <c r="G3">
-        <v>-13.54189030596884</v>
+        <v>-20.50172302518052</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.685598448009142</v>
       </c>
       <c r="E4">
-        <v>-21.12476726323886</v>
+        <v>-33.78365671156956</v>
       </c>
       <c r="F4">
-        <v>-3.479705700471932</v>
+        <v>-5.13345672668606</v>
       </c>
       <c r="G4">
-        <v>-12.90395480164236</v>
+        <v>-20.3738515484534</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.42321664944387</v>
       </c>
       <c r="E5">
-        <v>-21.92777891664901</v>
+        <v>-34.34236851345091</v>
       </c>
       <c r="F5">
-        <v>-3.366347763235834</v>
+        <v>-5.038669958253323</v>
       </c>
       <c r="G5">
-        <v>-12.93553409554147</v>
+        <v>-20.05643809742085</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.05504141785328</v>
       </c>
       <c r="E6">
-        <v>-22.51402157625999</v>
+        <v>-34.33569354276361</v>
       </c>
       <c r="F6">
-        <v>-3.326670621376543</v>
+        <v>-5.095250765334141</v>
       </c>
       <c r="G6">
-        <v>-12.7373317341053</v>
+        <v>-20.24074775450147</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.586635083952436</v>
       </c>
       <c r="E7">
-        <v>-23.18444856767356</v>
+        <v>-34.93185582468839</v>
       </c>
       <c r="F7">
-        <v>-3.333874104311288</v>
+        <v>-5.172979792208429</v>
       </c>
       <c r="G7">
-        <v>-12.62748783311229</v>
+        <v>-19.94279203487598</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-4.032329729016066</v>
       </c>
       <c r="E8">
-        <v>-22.56082788360327</v>
+        <v>-35.03132828474088</v>
       </c>
       <c r="F8">
-        <v>-3.278078589528324</v>
+        <v>-4.894514149348542</v>
       </c>
       <c r="G8">
-        <v>-12.33240235646935</v>
+        <v>-19.55698436827485</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.399530200942171</v>
       </c>
       <c r="E9">
-        <v>-24.05961692592193</v>
+        <v>-35.84900087275086</v>
       </c>
       <c r="F9">
-        <v>-3.240898975388474</v>
+        <v>-4.894842182840051</v>
       </c>
       <c r="G9">
-        <v>-12.08774642002613</v>
+        <v>-19.67216983449549</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.689495030688581</v>
       </c>
       <c r="E10">
-        <v>-24.19120985211082</v>
+        <v>-36.11177916246795</v>
       </c>
       <c r="F10">
-        <v>-3.064498136962319</v>
+        <v>-4.797536349135402</v>
       </c>
       <c r="G10">
-        <v>-11.90557372009112</v>
+        <v>-19.5062353604306</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-1.913449318624906</v>
       </c>
       <c r="E11">
-        <v>-24.8580955768504</v>
+        <v>-36.44394273093057</v>
       </c>
       <c r="F11">
-        <v>-3.037528151061973</v>
+        <v>-4.904491006347859</v>
       </c>
       <c r="G11">
-        <v>-11.44526884721977</v>
+        <v>-19.28671639626706</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-1.072923637399722</v>
       </c>
       <c r="E12">
-        <v>-25.28089655257654</v>
+        <v>-36.83762109031339</v>
       </c>
       <c r="F12">
-        <v>-3.054874164476594</v>
+        <v>-4.805041357804765</v>
       </c>
       <c r="G12">
-        <v>-11.42023119130626</v>
+        <v>-19.15635704456718</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-0.1640634269290418</v>
       </c>
       <c r="E13">
-        <v>-26.21024810232668</v>
+        <v>-37.1105046697786</v>
       </c>
       <c r="F13">
-        <v>-3.05654166805843</v>
+        <v>-4.775295512737637</v>
       </c>
       <c r="G13">
-        <v>-11.13841769173026</v>
+        <v>-18.63917534405839</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.7982301364792641</v>
       </c>
       <c r="E14">
-        <v>-27.14314091875082</v>
+        <v>-37.5308580053036</v>
       </c>
       <c r="F14">
-        <v>-2.636762344852766</v>
+        <v>-4.747835133334834</v>
       </c>
       <c r="G14">
-        <v>-10.68447899793094</v>
+        <v>-18.47953421706366</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.79943346845564</v>
       </c>
       <c r="E15">
-        <v>-27.86587631342699</v>
+        <v>-38.25070649779988</v>
       </c>
       <c r="F15">
-        <v>-2.681241532546086</v>
+        <v>-4.536679312156823</v>
       </c>
       <c r="G15">
-        <v>-10.62430321166361</v>
+        <v>-18.05955013358787</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>2.821814364352767</v>
       </c>
       <c r="E16">
-        <v>-27.55019186187829</v>
+        <v>-38.4631349492627</v>
       </c>
       <c r="F16">
-        <v>-2.448878677489005</v>
+        <v>-4.497629244421452</v>
       </c>
       <c r="G16">
-        <v>-10.13973535053494</v>
+        <v>-18.05203519521372</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>3.825744667434889</v>
       </c>
       <c r="E17">
-        <v>-28.87387839974235</v>
+        <v>-39.2109807323114</v>
       </c>
       <c r="F17">
-        <v>-2.131465684451693</v>
+        <v>-4.428574052621876</v>
       </c>
       <c r="G17">
-        <v>-9.64295157636637</v>
+        <v>-17.93156775358518</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>4.772176402869508</v>
       </c>
       <c r="E18">
-        <v>-29.33309283496417</v>
+        <v>-39.37063887616283</v>
       </c>
       <c r="F18">
-        <v>-2.069150918208698</v>
+        <v>-4.232936866367911</v>
       </c>
       <c r="G18">
-        <v>-9.57790266706523</v>
+        <v>-17.57309691677458</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>5.628417171130243</v>
       </c>
       <c r="E19">
-        <v>-29.74129853896359</v>
+        <v>-40.07934958683725</v>
       </c>
       <c r="F19">
-        <v>-1.828522613206483</v>
+        <v>-4.107227971156073</v>
       </c>
       <c r="G19">
-        <v>-9.640293208298335</v>
+        <v>-17.39316380089689</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>6.356667617092429</v>
       </c>
       <c r="E20">
-        <v>-30.47300031217496</v>
+        <v>-40.94351375324698</v>
       </c>
       <c r="F20">
-        <v>-1.718988419901707</v>
+        <v>-3.951634893520839</v>
       </c>
       <c r="G20">
-        <v>-9.435661767424904</v>
+        <v>-17.121243866665</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.931088835241148</v>
       </c>
       <c r="E21">
-        <v>-31.94841563590303</v>
+        <v>-40.93488474602536</v>
       </c>
       <c r="F21">
-        <v>-1.450927071620982</v>
+        <v>-3.893341022651032</v>
       </c>
       <c r="G21">
-        <v>-9.353881360968288</v>
+        <v>-17.1063563433749</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>7.342570631831486</v>
       </c>
       <c r="E22">
-        <v>-31.7716987304647</v>
+        <v>-41.72987647196792</v>
       </c>
       <c r="F22">
-        <v>-1.43407228007622</v>
+        <v>-3.683635672795323</v>
       </c>
       <c r="G22">
-        <v>-9.148723543354112</v>
+        <v>-16.8352657008006</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>7.586961795454907</v>
       </c>
       <c r="E23">
-        <v>-32.29004145080467</v>
+        <v>-42.26915885611936</v>
       </c>
       <c r="F23">
-        <v>-1.270864020907051</v>
+        <v>-3.749896781345255</v>
       </c>
       <c r="G23">
-        <v>-9.007687682290081</v>
+        <v>-16.72817120787795</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>7.671720403793935</v>
       </c>
       <c r="E24">
-        <v>-32.47022716733287</v>
+        <v>-41.89200036991653</v>
       </c>
       <c r="F24">
-        <v>-1.113881771137322</v>
+        <v>-3.437664398045052</v>
       </c>
       <c r="G24">
-        <v>-9.55187184748994</v>
+        <v>-16.77196475954419</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>7.617832006809889</v>
       </c>
       <c r="E25">
-        <v>-33.31821336035019</v>
+        <v>-41.92841382941221</v>
       </c>
       <c r="F25">
-        <v>-1.117524930974834</v>
+        <v>-3.464165527995414</v>
       </c>
       <c r="G25">
-        <v>-9.102226931255048</v>
+        <v>-17.05691831156419</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>7.450399821498358</v>
       </c>
       <c r="E26">
-        <v>-33.46312905706966</v>
+        <v>-42.02100753744704</v>
       </c>
       <c r="F26">
-        <v>-0.9786416805888717</v>
+        <v>-3.473079589616939</v>
       </c>
       <c r="G26">
-        <v>-9.056177242803786</v>
+        <v>-16.96298323716014</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>7.19628111103784</v>
       </c>
       <c r="E27">
-        <v>-32.91389308704935</v>
+        <v>-42.23723311436529</v>
       </c>
       <c r="F27">
-        <v>-1.011927139568161</v>
+        <v>-3.481786559387765</v>
       </c>
       <c r="G27">
-        <v>-9.166501172899999</v>
+        <v>-16.96243534187339</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>6.884010466675629</v>
       </c>
       <c r="E28">
-        <v>-33.41731901400806</v>
+        <v>-42.30642819720249</v>
       </c>
       <c r="F28">
-        <v>-0.8051351578680984</v>
+        <v>-3.472287670379862</v>
       </c>
       <c r="G28">
-        <v>-9.139404357661064</v>
+        <v>-17.46769742316804</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>6.540848305111904</v>
       </c>
       <c r="E29">
-        <v>-33.09960580610392</v>
+        <v>-42.2189403436113</v>
       </c>
       <c r="F29">
-        <v>-0.8224173869927045</v>
+        <v>-3.507523934592745</v>
       </c>
       <c r="G29">
-        <v>-9.318796199343092</v>
+        <v>-16.91697824107366</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>6.186956133893223</v>
       </c>
       <c r="E30">
-        <v>-33.15177609090928</v>
+        <v>-42.51513877150501</v>
       </c>
       <c r="F30">
-        <v>-0.9163285710806817</v>
+        <v>-3.29820129047713</v>
       </c>
       <c r="G30">
-        <v>-9.540672271930585</v>
+        <v>-16.99585695436511</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.836445040008301</v>
       </c>
       <c r="E31">
-        <v>-32.28687151899931</v>
+        <v>-42.21308955519339</v>
       </c>
       <c r="F31">
-        <v>-0.8900303911440057</v>
+        <v>-3.418671590233664</v>
       </c>
       <c r="G31">
-        <v>-9.174840437113422</v>
+        <v>-17.19004858988044</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.50130039893771</v>
       </c>
       <c r="E32">
-        <v>-32.32256042265375</v>
+        <v>-41.88332607795483</v>
       </c>
       <c r="F32">
-        <v>-0.9920438367987648</v>
+        <v>-3.534173342308208</v>
       </c>
       <c r="G32">
-        <v>-9.695910373358091</v>
+        <v>-17.31563247963993</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.184590482716045</v>
       </c>
       <c r="E33">
-        <v>-31.91201802606637</v>
+        <v>-41.64409132460362</v>
       </c>
       <c r="F33">
-        <v>-1.042459933667948</v>
+        <v>-3.619380041727568</v>
       </c>
       <c r="G33">
-        <v>-9.216007070894261</v>
+        <v>-17.35150058528516</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.880446488547752</v>
       </c>
       <c r="E34">
-        <v>-31.49439083189399</v>
+        <v>-40.8670753762345</v>
       </c>
       <c r="F34">
-        <v>-0.8764468224728995</v>
+        <v>-3.475181986085244</v>
       </c>
       <c r="G34">
-        <v>-10.34834937769212</v>
+        <v>-17.51442577345485</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>4.583172367750448</v>
       </c>
       <c r="E35">
-        <v>-30.52276597728225</v>
+        <v>-41.0757112307159</v>
       </c>
       <c r="F35">
-        <v>-1.054069502818183</v>
+        <v>-3.399253001577239</v>
       </c>
       <c r="G35">
-        <v>-9.77722068234813</v>
+        <v>-17.66784804065407</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>4.282519322267594</v>
       </c>
       <c r="E36">
-        <v>-30.79800889170546</v>
+        <v>-40.9618880365331</v>
       </c>
       <c r="F36">
-        <v>-1.035640813208103</v>
+        <v>-3.480804115648044</v>
       </c>
       <c r="G36">
-        <v>-9.742042825447834</v>
+        <v>-17.70874155442791</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>3.959256936365413</v>
       </c>
       <c r="E37">
-        <v>-30.31706683819483</v>
+        <v>-40.48945045720888</v>
       </c>
       <c r="F37">
-        <v>-1.044693212185896</v>
+        <v>-3.312155139377287</v>
       </c>
       <c r="G37">
-        <v>-9.437131649644339</v>
+        <v>-17.28502317558382</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>3.598560071656816</v>
       </c>
       <c r="E38">
-        <v>-29.91235938036634</v>
+        <v>-39.90861479556306</v>
       </c>
       <c r="F38">
-        <v>-0.9020176958299174</v>
+        <v>-3.532630093836793</v>
       </c>
       <c r="G38">
-        <v>-9.716905853168148</v>
+        <v>-17.70626526636454</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.189243581260325</v>
       </c>
       <c r="E39">
-        <v>-29.68572737017847</v>
+        <v>-39.57368432948175</v>
       </c>
       <c r="F39">
-        <v>-0.9752693968920749</v>
+        <v>-3.425793893162935</v>
       </c>
       <c r="G39">
-        <v>-9.958446566258914</v>
+        <v>-17.68233995375223</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.712493016101399</v>
       </c>
       <c r="E40">
-        <v>-29.89258127013784</v>
+        <v>-39.23423897481479</v>
       </c>
       <c r="F40">
-        <v>-1.117725395886311</v>
+        <v>-3.491405561669072</v>
       </c>
       <c r="G40">
-        <v>-9.920004511456897</v>
+        <v>-17.42118756888682</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.158101826023473</v>
       </c>
       <c r="E41">
-        <v>-29.12455207843695</v>
+        <v>-38.61668191744077</v>
       </c>
       <c r="F41">
-        <v>-0.9322025756205286</v>
+        <v>-3.337950500300464</v>
       </c>
       <c r="G41">
-        <v>-9.831076637180994</v>
+        <v>-17.65827559822726</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.526107559774789</v>
       </c>
       <c r="E42">
-        <v>-28.17073318362336</v>
+        <v>-38.46175150045335</v>
       </c>
       <c r="F42">
-        <v>-0.9597060301282778</v>
+        <v>-3.30398909352049</v>
       </c>
       <c r="G42">
-        <v>-10.0512841948167</v>
+        <v>-17.72944570623052</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>0.8066459596980274</v>
       </c>
       <c r="E43">
-        <v>-27.40566561392349</v>
+        <v>-38.13826448818943</v>
       </c>
       <c r="F43">
-        <v>-0.9262714650164842</v>
+        <v>-3.289496805808513</v>
       </c>
       <c r="G43">
-        <v>-10.186526601187</v>
+        <v>-17.69693283848934</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.0001472726905406582</v>
       </c>
       <c r="E44">
-        <v>-26.84655757056646</v>
+        <v>-37.59923796281942</v>
       </c>
       <c r="F44">
-        <v>-1.028090244331585</v>
+        <v>-3.395159209872603</v>
       </c>
       <c r="G44">
-        <v>-9.974552370307467</v>
+        <v>-17.49382755910951</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.8782905905340026</v>
       </c>
       <c r="E45">
-        <v>-26.22863823527183</v>
+        <v>-37.15492673555684</v>
       </c>
       <c r="F45">
-        <v>-1.116702362143854</v>
+        <v>-3.410823637459542</v>
       </c>
       <c r="G45">
-        <v>-9.93271038523662</v>
+        <v>-17.68548497201454</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.82191696606111</v>
       </c>
       <c r="E46">
-        <v>-25.88949628836339</v>
+        <v>-37.11795174528422</v>
       </c>
       <c r="F46">
-        <v>-0.9006169265517835</v>
+        <v>-3.273795930055851</v>
       </c>
       <c r="G46">
-        <v>-10.31497576811072</v>
+        <v>-18.05481770873948</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-2.815171002133901</v>
       </c>
       <c r="E47">
-        <v>-25.49806405208838</v>
+        <v>-36.4918404005097</v>
       </c>
       <c r="F47">
-        <v>-1.071280492346149</v>
+        <v>-3.333626422457851</v>
       </c>
       <c r="G47">
-        <v>-9.598262522131748</v>
+        <v>-17.94391608844666</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.826348099500524</v>
       </c>
       <c r="E48">
-        <v>-25.44020373969238</v>
+        <v>-36.07976964394474</v>
       </c>
       <c r="F48">
-        <v>-1.072050045663349</v>
+        <v>-3.284969777952213</v>
       </c>
       <c r="G48">
-        <v>-9.825385809398986</v>
+        <v>-17.70400416376122</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.835225589744204</v>
       </c>
       <c r="E49">
-        <v>-24.94774577678024</v>
+        <v>-36.05410451750627</v>
       </c>
       <c r="F49">
-        <v>-0.9838479697154666</v>
+        <v>-3.194919614328684</v>
       </c>
       <c r="G49">
-        <v>-9.881929927209738</v>
+        <v>-17.8538791814151</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.816607958724219</v>
       </c>
       <c r="E50">
-        <v>-24.30050910075995</v>
+        <v>-35.8849818629788</v>
       </c>
       <c r="F50">
-        <v>-0.9012257765928411</v>
+        <v>-3.209495567148345</v>
       </c>
       <c r="G50">
-        <v>-9.732892477577289</v>
+        <v>-17.77595887105728</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.734158452612861</v>
       </c>
       <c r="E51">
-        <v>-23.85902816975217</v>
+        <v>-34.89819341315238</v>
       </c>
       <c r="F51">
-        <v>-0.784995061203834</v>
+        <v>-3.269625100182755</v>
       </c>
       <c r="G51">
-        <v>-10.11120837962304</v>
+        <v>-17.86955130399801</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-7.564998096462606</v>
       </c>
       <c r="E52">
-        <v>-23.13985668412003</v>
+        <v>-34.64903677325035</v>
       </c>
       <c r="F52">
-        <v>-1.176511316993381</v>
+        <v>-3.332544574629794</v>
       </c>
       <c r="G52">
-        <v>-9.837522269345955</v>
+        <v>-18.21162169820705</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.287812380014584</v>
       </c>
       <c r="E53">
-        <v>-22.68348613057503</v>
+        <v>-34.7290028315148</v>
       </c>
       <c r="F53">
-        <v>-0.9912038722523262</v>
+        <v>-3.287462335467237</v>
       </c>
       <c r="G53">
-        <v>-10.22466408579941</v>
+        <v>-18.01671829540077</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.877288699218925</v>
       </c>
       <c r="E54">
-        <v>-22.30217503370716</v>
+        <v>-33.77867086168712</v>
       </c>
       <c r="F54">
-        <v>-1.096698117733649</v>
+        <v>-3.206220202437676</v>
       </c>
       <c r="G54">
-        <v>-10.0090250810079</v>
+        <v>-18.01577644519485</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.321167277275686</v>
       </c>
       <c r="E55">
-        <v>-22.35910248045759</v>
+        <v>-33.98594817396621</v>
       </c>
       <c r="F55">
-        <v>-1.140005165552007</v>
+        <v>-3.429615980359451</v>
       </c>
       <c r="G55">
-        <v>-10.18074638867543</v>
+        <v>-18.27097150336234</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.613479691573509</v>
       </c>
       <c r="E56">
-        <v>-21.5898415438266</v>
+        <v>-33.76430654213479</v>
       </c>
       <c r="F56">
-        <v>-1.035655723821353</v>
+        <v>-3.181127297072073</v>
       </c>
       <c r="G56">
-        <v>-10.35580803679209</v>
+        <v>-18.09201996423704</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.750124174500463</v>
       </c>
       <c r="E57">
-        <v>-20.22211559623794</v>
+        <v>-33.57385930350521</v>
       </c>
       <c r="F57">
-        <v>-0.8868221241929632</v>
+        <v>-3.292915478079866</v>
       </c>
       <c r="G57">
-        <v>-10.27996343848739</v>
+        <v>-17.94191486366817</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-9.737334586200221</v>
       </c>
       <c r="E58">
-        <v>-20.94078442125523</v>
+        <v>-32.87297379591605</v>
       </c>
       <c r="F58">
-        <v>-1.145267783661992</v>
+        <v>-3.360888822051385</v>
       </c>
       <c r="G58">
-        <v>-10.24025675528937</v>
+        <v>-18.48630924850977</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-9.587173996886328</v>
       </c>
       <c r="E59">
-        <v>-20.76515661381575</v>
+        <v>-32.86821663397099</v>
       </c>
       <c r="F59">
-        <v>-1.008806679561816</v>
+        <v>-3.316369872722731</v>
       </c>
       <c r="G59">
-        <v>-10.32986329140083</v>
+        <v>-18.12804863134092</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.31732695704425</v>
       </c>
       <c r="E60">
-        <v>-20.40106277512504</v>
+        <v>-32.49969168346378</v>
       </c>
       <c r="F60">
-        <v>-1.216925705841164</v>
+        <v>-3.385483878607905</v>
       </c>
       <c r="G60">
-        <v>-10.82082050542028</v>
+        <v>-18.53998312333798</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.948515918596682</v>
       </c>
       <c r="E61">
-        <v>-20.31449193752041</v>
+        <v>-32.28490616127997</v>
       </c>
       <c r="F61">
-        <v>-1.35650561321288</v>
+        <v>-3.333370456930385</v>
       </c>
       <c r="G61">
-        <v>-10.81544749001005</v>
+        <v>-18.22789634007811</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.50272385895475</v>
       </c>
       <c r="E62">
-        <v>-19.60862510852281</v>
+        <v>-32.30905651316288</v>
       </c>
       <c r="F62">
-        <v>-1.280248595213366</v>
+        <v>-3.46645182202714</v>
       </c>
       <c r="G62">
-        <v>-10.4373600156065</v>
+        <v>-18.66848856953587</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.008759400153664</v>
       </c>
       <c r="E63">
-        <v>-19.67957723927499</v>
+        <v>-32.0751019605046</v>
       </c>
       <c r="F63">
-        <v>-1.311003391777103</v>
+        <v>-3.513482381321082</v>
       </c>
       <c r="G63">
-        <v>-10.87187573872692</v>
+        <v>-18.32207805012484</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.489746127721125</v>
       </c>
       <c r="E64">
-        <v>-19.51969493596018</v>
+        <v>-32.20792210314958</v>
       </c>
       <c r="F64">
-        <v>-1.373400994760379</v>
+        <v>-3.333127745281365</v>
       </c>
       <c r="G64">
-        <v>-10.47726533153688</v>
+        <v>-18.5154288070732</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.964732108254582</v>
       </c>
       <c r="E65">
-        <v>-19.38396298452827</v>
+        <v>-31.92469548905085</v>
       </c>
       <c r="F65">
-        <v>-1.544049649941494</v>
+        <v>-3.531876279500245</v>
       </c>
       <c r="G65">
-        <v>-10.59822935499631</v>
+        <v>-18.74703126245507</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.459436173805811</v>
       </c>
       <c r="E66">
-        <v>-18.81398207507884</v>
+        <v>-31.72621247329466</v>
       </c>
       <c r="F66">
-        <v>-1.41299529987939</v>
+        <v>-3.6540687550872</v>
       </c>
       <c r="G66">
-        <v>-10.79635888443061</v>
+        <v>-18.75438729464334</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.987900424256702</v>
       </c>
       <c r="E67">
-        <v>-19.20374783291902</v>
+        <v>-31.97818355979244</v>
       </c>
       <c r="F67">
-        <v>-1.701789027517381</v>
+        <v>-3.761380438650265</v>
       </c>
       <c r="G67">
-        <v>-10.93015458240025</v>
+        <v>-18.7122937081115</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.557577674103372</v>
       </c>
       <c r="E68">
-        <v>-19.2941814588522</v>
+        <v>-31.62300628642284</v>
       </c>
       <c r="F68">
-        <v>-1.532347303642145</v>
+        <v>-3.780770862814996</v>
       </c>
       <c r="G68">
-        <v>-10.65510121681545</v>
+        <v>-18.25961136634433</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.181750985908832</v>
       </c>
       <c r="E69">
-        <v>-18.41192603878183</v>
+        <v>-31.69029941017682</v>
       </c>
       <c r="F69">
-        <v>-1.662772922845525</v>
+        <v>-3.742281599811319</v>
       </c>
       <c r="G69">
-        <v>-10.44128632261608</v>
+        <v>-18.44777118788712</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.859830627537994</v>
       </c>
       <c r="E70">
-        <v>-18.50909350556442</v>
+        <v>-31.58242663084011</v>
       </c>
       <c r="F70">
-        <v>-1.619505636662501</v>
+        <v>-3.845268377164368</v>
       </c>
       <c r="G70">
-        <v>-10.59233327339086</v>
+        <v>-18.4287471379457</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.583352352828874</v>
       </c>
       <c r="E71">
-        <v>-18.14920661922684</v>
+        <v>-31.5846048268378</v>
       </c>
       <c r="F71">
-        <v>-1.822617181991926</v>
+        <v>-3.873741849900795</v>
       </c>
       <c r="G71">
-        <v>-10.66339413339132</v>
+        <v>-18.28232501928927</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.349204635728175</v>
       </c>
       <c r="E72">
-        <v>-19.39470452487447</v>
+        <v>-31.96986475304035</v>
       </c>
       <c r="F72">
-        <v>-2.158780271191604</v>
+        <v>-4.014561823274503</v>
       </c>
       <c r="G72">
-        <v>-10.29787348985485</v>
+        <v>-18.34440271396891</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.142248658324096</v>
       </c>
       <c r="E73">
-        <v>-18.85753693808461</v>
+        <v>-31.37351227520725</v>
       </c>
       <c r="F73">
-        <v>-1.959400521011791</v>
+        <v>-4.117815334931253</v>
       </c>
       <c r="G73">
-        <v>-10.36982488660537</v>
+        <v>-18.38944765184901</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.940577317670222</v>
       </c>
       <c r="E74">
-        <v>-19.11177905429725</v>
+        <v>-31.70552187555361</v>
       </c>
       <c r="F74">
-        <v>-1.998078651783306</v>
+        <v>-4.118419214767894</v>
       </c>
       <c r="G74">
-        <v>-9.780577575524951</v>
+        <v>-18.00330562014842</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.730019905469179</v>
       </c>
       <c r="E75">
-        <v>-19.05405006764747</v>
+        <v>-32.05311621919736</v>
       </c>
       <c r="F75">
-        <v>-2.127175569672595</v>
+        <v>-4.059576136310031</v>
       </c>
       <c r="G75">
-        <v>-9.998494235647478</v>
+        <v>-18.12587360292162</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.492305229147831</v>
       </c>
       <c r="E76">
-        <v>-19.81537711781701</v>
+        <v>-31.69312517795761</v>
       </c>
       <c r="F76">
-        <v>-2.321134483568488</v>
+        <v>-4.305377595742728</v>
       </c>
       <c r="G76">
-        <v>-9.545250756411397</v>
+        <v>-18.13662294428764</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.207450641071119</v>
       </c>
       <c r="E77">
-        <v>-20.10320239727053</v>
+        <v>-32.10386909163833</v>
       </c>
       <c r="F77">
-        <v>-2.504909448614363</v>
+        <v>-4.453174079382813</v>
       </c>
       <c r="G77">
-        <v>-9.650327471827865</v>
+        <v>-17.76190229469753</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.867449894870105</v>
       </c>
       <c r="E78">
-        <v>-20.14483265882304</v>
+        <v>-32.76081934440508</v>
       </c>
       <c r="F78">
-        <v>-2.562017925730764</v>
+        <v>-4.384322665964326</v>
       </c>
       <c r="G78">
-        <v>-9.408753653281707</v>
+        <v>-17.61562915059037</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.46735583182839</v>
       </c>
       <c r="E79">
-        <v>-20.1811781912086</v>
+        <v>-32.45543264274981</v>
       </c>
       <c r="F79">
-        <v>-2.436258500107355</v>
+        <v>-4.530030007014552</v>
       </c>
       <c r="G79">
-        <v>-9.698055606867538</v>
+        <v>-17.52791790180015</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.002664146840947</v>
       </c>
       <c r="E80">
-        <v>-20.83617214320403</v>
+        <v>-32.72514629040965</v>
       </c>
       <c r="F80">
-        <v>-2.52118272624236</v>
+        <v>-4.448951890730744</v>
       </c>
       <c r="G80">
-        <v>-9.148183924431212</v>
+        <v>-17.54433324185663</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.481991423320602</v>
       </c>
       <c r="E81">
-        <v>-21.31379935374104</v>
+        <v>-33.4047660840588</v>
       </c>
       <c r="F81">
-        <v>-2.406694895868843</v>
+        <v>-4.558753646706625</v>
       </c>
       <c r="G81">
-        <v>-8.86683059068517</v>
+        <v>-17.21479160724096</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.9195517500262884</v>
       </c>
       <c r="E82">
-        <v>-21.6489381296267</v>
+        <v>-33.68406424695588</v>
       </c>
       <c r="F82">
-        <v>-2.346366554657761</v>
+        <v>-4.425827186314193</v>
       </c>
       <c r="G82">
-        <v>-8.965683480487808</v>
+        <v>-17.56593786204591</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.3278310452822346</v>
       </c>
       <c r="E83">
-        <v>-22.52786059282743</v>
+        <v>-33.85724667843122</v>
       </c>
       <c r="F83">
-        <v>-2.448454553378772</v>
+        <v>-4.526600565966961</v>
       </c>
       <c r="G83">
-        <v>-8.393511963298952</v>
+        <v>-17.49502928714026</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.2712942620738311</v>
       </c>
       <c r="E84">
-        <v>-23.32107262848498</v>
+        <v>-34.63137119614643</v>
       </c>
       <c r="F84">
-        <v>-2.749233100600466</v>
+        <v>-4.45220240441933</v>
       </c>
       <c r="G84">
-        <v>-8.480238324791239</v>
+        <v>-17.41496374327299</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.8536964093291898</v>
       </c>
       <c r="E85">
-        <v>-23.96829119060924</v>
+        <v>-35.34834184341084</v>
       </c>
       <c r="F85">
-        <v>-2.555929425320188</v>
+        <v>-4.568314663269736</v>
       </c>
       <c r="G85">
-        <v>-8.318392374467349</v>
+        <v>-17.02039968372049</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.40065525262691</v>
       </c>
       <c r="E86">
-        <v>-24.96815560913281</v>
+        <v>-35.85664946534981</v>
       </c>
       <c r="F86">
-        <v>-2.771998293564203</v>
+        <v>-4.739763521361955</v>
       </c>
       <c r="G86">
-        <v>-8.297678291028129</v>
+        <v>-17.29711659843878</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.890016953434393</v>
       </c>
       <c r="E87">
-        <v>-26.11039072198354</v>
+        <v>-36.40010483829932</v>
       </c>
       <c r="F87">
-        <v>-2.783600407407812</v>
+        <v>-4.695524560215448</v>
       </c>
       <c r="G87">
-        <v>-8.242792756532552</v>
+        <v>-17.25860833272598</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.301265510411552</v>
       </c>
       <c r="E88">
-        <v>-27.06699462831184</v>
+        <v>-36.96375494108604</v>
       </c>
       <c r="F88">
-        <v>-2.733335901773341</v>
+        <v>-4.658319266686111</v>
       </c>
       <c r="G88">
-        <v>-7.926092728063714</v>
+        <v>-16.99302312738349</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.620611698114671</v>
       </c>
       <c r="E89">
-        <v>-28.28846897934878</v>
+        <v>-37.85953464878031</v>
       </c>
       <c r="F89">
-        <v>-2.630504029124616</v>
+        <v>-4.814048196575404</v>
       </c>
       <c r="G89">
-        <v>-7.741003437508601</v>
+        <v>-17.02020767207921</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.833983050942447</v>
       </c>
       <c r="E90">
-        <v>-29.65051622053183</v>
+        <v>-38.77928356939719</v>
       </c>
       <c r="F90">
-        <v>-2.67693153694932</v>
+        <v>-4.942121252354832</v>
       </c>
       <c r="G90">
-        <v>-8.029524102347164</v>
+        <v>-17.19382592234075</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.932163320598971</v>
       </c>
       <c r="E91">
-        <v>-30.68546951990384</v>
+        <v>-39.66200542229035</v>
       </c>
       <c r="F91">
-        <v>-2.991686298991048</v>
+        <v>-4.744588761483262</v>
       </c>
       <c r="G91">
-        <v>-8.282800699374645</v>
+        <v>-16.72250686446025</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.910998720258314</v>
       </c>
       <c r="E92">
-        <v>-32.55768785008001</v>
+        <v>-40.80477715931099</v>
       </c>
       <c r="F92">
-        <v>-3.034687679237773</v>
+        <v>-5.077048220025024</v>
       </c>
       <c r="G92">
-        <v>-7.926460198618573</v>
+        <v>-17.21120463114915</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.770000448889119</v>
       </c>
       <c r="E93">
-        <v>-33.45189617729363</v>
+        <v>-41.74581896471193</v>
       </c>
       <c r="F93">
-        <v>-3.219083091468346</v>
+        <v>-5.197491183657267</v>
       </c>
       <c r="G93">
-        <v>-8.208296872013346</v>
+        <v>-17.30217676729556</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.515350423558659</v>
       </c>
       <c r="E94">
-        <v>-35.17706589949273</v>
+        <v>-42.66985408597706</v>
       </c>
       <c r="F94">
-        <v>-3.264834651492366</v>
+        <v>-5.127287046270009</v>
       </c>
       <c r="G94">
-        <v>-8.287991634780221</v>
+        <v>-17.16810794931892</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.15796420984355</v>
       </c>
       <c r="E95">
-        <v>-36.94036763707342</v>
+        <v>-43.82252506717846</v>
       </c>
       <c r="F95">
-        <v>-3.416640433362</v>
+        <v>-5.164134485081337</v>
       </c>
       <c r="G95">
-        <v>-8.797494524910675</v>
+        <v>-17.07712919208144</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.708921396854989</v>
       </c>
       <c r="E96">
-        <v>-38.64146625568475</v>
+        <v>-45.87832094091458</v>
       </c>
       <c r="F96">
-        <v>-3.455150405550746</v>
+        <v>-5.30779990048366</v>
       </c>
       <c r="G96">
-        <v>-8.615656190075127</v>
+        <v>-17.39403116382818</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.195733815139547</v>
       </c>
       <c r="E97">
-        <v>-40.58725417458954</v>
+        <v>-46.91832575304215</v>
       </c>
       <c r="F97">
-        <v>-3.362328524597451</v>
+        <v>-5.481651024043998</v>
       </c>
       <c r="G97">
-        <v>-9.534335887768421</v>
+        <v>-18.19859304623725</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.627878003274967</v>
       </c>
       <c r="E98">
-        <v>-42.40890077128506</v>
+        <v>-48.06722451539516</v>
       </c>
       <c r="F98">
-        <v>-3.62169450025099</v>
+        <v>-5.291321187739769</v>
       </c>
       <c r="G98">
-        <v>-9.033460279313308</v>
+        <v>-17.71115494212604</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.04543328082854132</v>
       </c>
       <c r="E99">
-        <v>-44.41457549470428</v>
+        <v>-49.73658758816074</v>
       </c>
       <c r="F99">
-        <v>-3.572733016541122</v>
+        <v>-5.583242002323329</v>
       </c>
       <c r="G99">
-        <v>-9.529545528373095</v>
+        <v>-18.20930597160234</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.5555356266129505</v>
       </c>
       <c r="E100">
-        <v>-46.12283363072174</v>
+        <v>-50.92723208815346</v>
       </c>
       <c r="F100">
-        <v>-3.850661877323996</v>
+        <v>-5.800133439398324</v>
       </c>
       <c r="G100">
-        <v>-9.888276243008521</v>
+        <v>-18.50788572906198</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-1.114432824129698</v>
       </c>
       <c r="E101">
-        <v>-48.32966543379869</v>
+        <v>-52.38587847263113</v>
       </c>
       <c r="F101">
-        <v>-4.057887923543126</v>
+        <v>-5.776660820672597</v>
       </c>
       <c r="G101">
-        <v>-10.10235267030549</v>
+        <v>-18.6604406333299</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.693228896610541</v>
       </c>
       <c r="E102">
-        <v>-50.23860742394007</v>
+        <v>-54.1919776859398</v>
       </c>
       <c r="F102">
-        <v>-3.975077691020064</v>
+        <v>-5.783315096019286</v>
       </c>
       <c r="G102">
-        <v>-10.44368977867759</v>
+        <v>-18.48177049057543</v>
       </c>
     </row>
   </sheetData>
